--- a/data/price-comparison-sheet.xlsx
+++ b/data/price-comparison-sheet.xlsx
@@ -279,7 +279,7 @@
     </comment>
     <comment ref="K19" authorId="0" shapeId="0">
       <text>
-        <t>Confirmed: 'No contract and no early termination charges' - Keppel Electric residential price plan page https://www.keppelelectric.com/residential-price-plan</t>
+        <t>Source: Keppel Electric Terms &amp; Conditions (Clause on 'Early Termination Fees') http://portal.keppelelectric.com/termsandconditions . Historically illustrated as ~30% of remaining bill value (2019 estimate, moneysmart/yahoo review) - actual formula per T&amp;Cs is days-remaining x average daily charge, uncapped.</t>
       </text>
     </comment>
     <comment ref="K20" authorId="0" shapeId="0">
@@ -294,7 +294,7 @@
     </comment>
     <comment ref="K22" authorId="0" shapeId="0">
       <text>
-        <t>Source: Keppel Electric Terms &amp; Conditions (Clause on 'Early Termination Fees') http://portal.keppelelectric.com/termsandconditions . Historically illustrated as ~30% of remaining bill value (2019 estimate, moneysmart/yahoo review) - actual formula per T&amp;Cs is days-remaining x average daily charge, uncapped.</t>
+        <t>Source: Tuas Power Supply, Conditions of Supply of Electricity Agreement https://www.savewithtuas.com/assets/pdf/nsp_20220215.pdf and FAQ https://www.savewithtuas.com/faq/ (S$200 GST n/a). Confirmed for PowerFIX plans generally; PowerFIX 25 G+ and PowerDOT 6 assumed same flat $200 standard fee - not separately verified.</t>
       </text>
     </comment>
     <comment ref="K23" authorId="0" shapeId="0">
@@ -314,12 +314,12 @@
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
       <text>
-        <t>Source: Tuas Power Supply, Conditions of Supply of Electricity Agreement https://www.savewithtuas.com/assets/pdf/nsp_20220215.pdf and FAQ https://www.savewithtuas.com/faq/ (S$200 GST n/a). Confirmed for PowerFIX plans generally; PowerFIX 25 G+ and PowerDOT 6 assumed same flat $200 standard fee - not separately verified.</t>
+        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
       </text>
     </comment>
     <comment ref="K27" authorId="0" shapeId="0">
       <text>
-        <t>Source: Tuas Power Supply, Conditions of Supply of Electricity Agreement https://www.savewithtuas.com/assets/pdf/nsp_20220215.pdf and FAQ https://www.savewithtuas.com/faq/ (S$200 GST n/a). Confirmed for PowerFIX plans generally; PowerFIX 25 G+ and PowerDOT 6 assumed same flat $200 standard fee - not separately verified.</t>
+        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
       </text>
     </comment>
     <comment ref="K28" authorId="0" shapeId="0">
@@ -349,55 +349,45 @@
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
+        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
       </text>
     </comment>
     <comment ref="K34" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
+        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
       </text>
     </comment>
     <comment ref="K35" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
+        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
       </text>
     </comment>
     <comment ref="K36" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
+        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
       </text>
     </comment>
     <comment ref="K37" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
+        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
       </text>
     </comment>
     <comment ref="K38" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
+        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
       </text>
     </comment>
     <comment ref="K39" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
+        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
       <text>
-        <t>Source: PacificLight 'Recontract' page https://www.pacificlight.com.sg/recontract/ : 'No early termination charge for Easy Peasy, Easy Save and 9-to-9 plans.'</t>
+        <t>Could not locate a current, live Sembcorp Power factsheet with exact figures (their factsheet PDF links returned 404). Indicative structure/example only, from a 2022 review (Yahoo/AsiaOne, moneysmart) citing ~$32.10/month for a 4-room HDB flat on the (then) 24-month plan - this figure is dated and NOT verified current. Recommend pulling the exact rate from Sembcorp Power's live factsheet before relying on this.</t>
       </text>
     </comment>
     <comment ref="K41" authorId="0" shapeId="0">
-      <text>
-        <t>Source: PacificLight factsheets - Savvy Saver 24 (11 Nov 2025) https://pacificlight.com.sg/pdf/Factsheet_SavvySaver24_Excl_11112025.pdf and Classic 60 factsheet https://pacificlight.com.sg/support/factsheet-recontract-detail/09-classic-60-07-aug-2024 (same table). Confirmed directly for Savvy Saver 24, Stack It Up 24 (per MissLobang Aug 2026 review) and Classic 60; assumed same standard dwelling-type table for Savvy Saver 12/36, Sunny Side-Up 12, and Save While Sleeping 24 - not individually fetched per plan.</t>
-      </text>
-    </comment>
-    <comment ref="K42" authorId="0" shapeId="0">
-      <text>
-        <t>Could not locate a current, live Sembcorp Power factsheet with exact figures (their factsheet PDF links returned 404). Indicative structure/example only, from a 2022 review (Yahoo/AsiaOne, moneysmart) citing ~$32.10/month for a 4-room HDB flat on the (then) 24-month plan - this figure is dated and NOT verified current. Recommend pulling the exact rate from Sembcorp Power's live factsheet before relying on this.</t>
-      </text>
-    </comment>
-    <comment ref="K43" authorId="0" shapeId="0">
       <text>
         <t>Could not locate a current, live Sembcorp Power factsheet with exact figures (their factsheet PDF links returned 404). Indicative structure/example only, from a 2022 review (Yahoo/AsiaOne, moneysmart) citing ~$32.10/month for a 4-room HDB flat on the (then) 24-month plan - this figure is dated and NOT verified current. Recommend pulling the exact rate from Sembcorp Power's live factsheet before relying on this.</t>
       </text>
@@ -695,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -804,7 +794,7 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -860,7 +850,7 @@
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -1084,7 +1074,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -1140,7 +1130,7 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1196,7 +1186,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>29.4</v>
+        <v>28.9</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1252,7 +1242,7 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>30.18</v>
+        <v>29.68</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -1536,7 +1526,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1592,7 +1582,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>29.3</v>
+        <v>28.5</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1648,7 +1638,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>29.4</v>
+        <v>28.9</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1704,7 +1694,7 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>34.77</v>
+        <v>31.15</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1731,394 +1721,392 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Keppel Electric</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>SURESAVE DOT</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>WEEKEND SAVER</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Discount off Tariff</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Time of Use</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Nights + Weekends</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Days left in contract × your average daily charge over the past 12 months</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>WEEKEND SAVER</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Time of Use</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>09:00–21:00 (weekdays only)</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>None (no lock-in)</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Days left in contract × your average daily charge over the past 12 months</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Keppel Electric</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Keppel Electric</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>WEEKEND SAVER</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ecoGreen24</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Days left in contract × your average daily charge over the past 12 months</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>PowerFIX 24</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Time of Use</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Nights + Weekends</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>Keppel Electric</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Keppel Electric</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>WEEKEND SAVER</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>No separate deposit; existing SP Group deposit carries over</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>$200 flat (all Tuas Power residential plans)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>PowerFIX 12</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Time of Use</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>09:00–21:00 (weekdays only)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Keppel Electric</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Keppel Electric</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ecoGreen24</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>No separate deposit; existing SP Group deposit carries over</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>$200 flat (all Tuas Power residential plans)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>PowerFIX 36</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>No separate deposit; existing SP Group deposit carries over</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>$200 flat (all Tuas Power residential plans)</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>PowerFIX 25 G+</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
+      <c r="E25" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Keppel Electric</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>PowerFIX 24</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>No separate deposit; existing SP Group deposit carries over</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>$200 flat (all Tuas Power residential plans)</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>PowerFIX 12</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>No separate deposit; existing SP Group deposit carries over</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>$200 flat (all Tuas Power residential plans)</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>PowerFIX 36</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>No separate deposit; existing SP Group deposit carries over</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>$200 flat (all Tuas Power residential plans)</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Tuas Power</t>
         </is>
@@ -2127,17 +2115,17 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Tuas Power</t>
+          <t>PacificLight</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PowerFIX 25 G+</t>
+          <t>Savvy Saver 24</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2146,7 +2134,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2154,7 +2142,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>32.7</v>
+        <v>29</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -2166,29 +2154,29 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>No separate deposit; existing SP Group deposit carries over</t>
+          <t>Varies by residential dwelling type</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>$200 flat (all Tuas Power residential plans)</t>
+          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Tuas Power</t>
+          <t>PacificLight</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Tuas Power</t>
+          <t>PacificLight</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>PowerDOT 6</t>
+          <t>Savvy Saver 12</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2198,25 +2186,23 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Discount off Tariff</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G27" s="5" t="n">
+        <v>30.5</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" s="5" t="n">
@@ -2224,17 +2210,17 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>No separate deposit; existing SP Group deposit carries over</t>
+          <t>Varies by residential dwelling type</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>$200 flat (all Tuas Power residential plans)</t>
+          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>Tuas Power</t>
+          <t>PacificLight</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2232,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Savvy Saver 24</t>
+          <t>Savvy Saver 36</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2260,7 +2246,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2268,7 +2254,7 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>29.8</v>
+        <v>28.9</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -2302,12 +2288,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Savvy Saver 12</t>
+          <t>Sunny Side-Up 12</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2358,7 +2344,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Savvy Saver 36</t>
+          <t>Stack It Up 24</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2368,19 +2354,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Tiered</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0–300 kWh</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -2414,29 +2400,29 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Sunny Side-Up 12</t>
+          <t>Stack It Up 24</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Tiered</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301–600 kWh</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>31.5</v>
+        <v>28.6</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -2488,11 +2474,11 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>0–300 kWh</t>
+          <t>&gt;600 kWh</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>30</v>
+        <v>27.6</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -2526,7 +2512,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Stack It Up 24</t>
+          <t>Easy Peasy</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2536,19 +2522,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Tiered</t>
+          <t>Fixed + Daily Charge</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>301–600 kWh</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>29.4</v>
+        <v>27</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -2556,7 +2542,7 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2565,7 +2551,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
+          <t>None (no lock-in)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2582,7 +2568,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Stack It Up 24</t>
+          <t>Easy Save</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2592,27 +2578,29 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tiered</t>
+          <t>Discount off Tariff + Daily Charge</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>&gt;600 kWh</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>28</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2621,7 +2609,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
+          <t>None (no lock-in)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2638,7 +2626,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Easy Peasy</t>
+          <t>Save While Sleeping 24</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2648,28 +2636,28 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Fixed + Daily Charge</t>
+          <t>Time of Use</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>23:00–07:00</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.55</v>
-      </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Varies by residential dwelling type</t>
@@ -2677,7 +2665,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>None (no lock-in)</t>
+          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2694,7 +2682,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Easy Save</t>
+          <t>Save While Sleeping 24</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2704,30 +2692,28 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Discount off Tariff + Daily Charge</t>
+          <t>Time of Use</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>07:00–23:00</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.55</v>
-      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Varies by residential dwelling type</t>
@@ -2735,7 +2721,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>None (no lock-in)</t>
+          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2752,7 +2738,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Save While Sleeping 24</t>
+          <t>9 to 9</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2762,19 +2748,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Time of Use</t>
+          <t>Time of Use + Daily Charge</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>23:00–07:00</t>
+          <t>21:00–09:00</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>22.5</v>
+        <v>20.05</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -2782,7 +2768,7 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2791,7 +2777,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
+          <t>None (no lock-in)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2808,7 +2794,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Save While Sleeping 24</t>
+          <t>9 to 9</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2818,19 +2804,19 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Time of Use</t>
+          <t>Time of Use + Daily Charge</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>07:00–23:00</t>
+          <t>09:00–21:00</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>34.5</v>
+        <v>36.95</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2824,7 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -2847,7 +2833,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
+          <t>None (no lock-in)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -2864,7 +2850,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>9 to 9</t>
+          <t>Classic 60</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2874,28 +2860,30 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Time of Use + Daily Charge</t>
+          <t>Discount off Tariff</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>21:00–09:00</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Varies by residential dwelling type</t>
@@ -2903,7 +2891,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>None (no lock-in)</t>
+          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2915,12 +2903,12 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PacificLight</t>
+          <t>Sembcorp Power</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>9 to 9</t>
+          <t>24M Fixed Price Plan Home</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2930,53 +2918,53 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Time of Use + Daily Charge</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>09:00–21:00</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Varies by residential dwelling type</t>
+          <t>$50–$200 depending on dwelling type</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>None (no lock-in)</t>
+          <t>Charged per remaining month; amount depends on home type (see retailer terms)</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>PacificLight</t>
+          <t>Sembcorp Power</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>PacificLight</t>
+          <t>Sembcorp Power</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Classic 60</t>
+          <t>12M Fixed Price Plan Home</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2986,25 +2974,23 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Discount off Tariff</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G41" s="5" t="n">
+        <v>31</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>8*</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="5" t="n">
@@ -3012,29 +2998,29 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Varies by residential dwelling type</t>
+          <t>$50–$200 depending on dwelling type</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>HDB1-2rm $160; HDB3rm $220; HDB4rm $320; HDB5rm $380; HDB Exec/Jumbo/Multi-Gen $460; Condo/Apt/Shophouse $480; Terrace $720; Semi-D $1,000; Bungalow/Penthouse $2,000</t>
+          <t>Charged per remaining month; amount depends on home type (see retailer terms)</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>PacificLight</t>
+          <t>Sembcorp Power</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Sembcorp Power</t>
+          <t>SP Group</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24M Fixed Price Plan Home</t>
+          <t>Regulated Tariff</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3044,11 +3030,11 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Regulated</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3056,7 +3042,7 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>29.8</v>
+        <v>31.16</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -3068,216 +3054,106 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>$50–$200 depending on dwelling type</t>
+          <t>Varies by dwelling type, payment method and citizenship</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Charged per remaining month; amount depends on home type (see retailer terms)</t>
+          <t>N/A - regulated tariff, no fixed contract</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Sembcorp Power</t>
+          <t>SP Group</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Sembcorp Power</t>
+          <t>Flo Energy</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>12M Fixed Price Plan Home</t>
+          <t>Residential (not yet launched)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>12</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="5" t="n">
-        <v>31</v>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>0</v>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>$50–$200 depending on dwelling type</t>
+          <t>Not yet available</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Charged per remaining month; amount depends on home type (see retailer terms)</t>
+          <t>N/A - plan not yet launched</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>Sembcorp Power</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SP Group</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Regulated Tariff</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Regulated</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>31.16</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Varies by dwelling type, payment method and citizenship</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>N/A - regulated tariff, no fixed contract</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>SP Group</t>
-        </is>
-      </c>
-    </row>
+          <t>Flo Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1"/>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Flo Energy</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Residential (not yet launched)</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>Not yet available</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>N/A - plan not yet launched</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>Flo Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>* Discount (%) marked with an asterisk denotes a cents-off-tariff figure (not a true percentage) as published by the retailer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Security Deposit Note: Deposit amounts may vary according to residential type, customer status and/or payment arrangement.</t>
+        </is>
+      </c>
+    </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>* Discount (%) marked with an asterisk denotes a cents-off-tariff figure (not a true percentage) as published by the retailer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Security Deposit Note: Deposit amounts may vary according to residential type, customer status and/or payment arrangement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
           <t>This sheet only includes product rates and other fact sheet information, for more information on promotions, please check the promotions sheet.</t>
         </is>
       </c>
     </row>
+    <row r="48" ht="30" customHeight="1"/>
+    <row r="49" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -3291,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3380,7 +3256,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SP customers use GENECO200; all other customers use GENECO100</t>
+          <t>Sign up online. Current SP Group customers use GENECO200; everyone else GENECO100. The 29.00¢ rate is for the first 1,000 sign-ups</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3395,7 +3271,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16 Oct 2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -3405,7 +3281,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3427,12 +3303,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GENECO15</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Limited sign-ups; promo code required (ask us for it)</t>
+          <t>Sign up online; first 250 customers</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -3447,7 +3323,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -3457,7 +3333,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3474,22 +3350,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates bundle</t>
+          <t>Gifts &amp; bill rebates</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MBFC130 / TGBGN130</t>
+          <t>GIROBCRC / MBBC130 / TGBGN130 / GIROBC100 / BC60</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The $130 cash-only rebate needs the promo code; the higher total includes gift options</t>
+          <t>Gift options need GIRO; cash-only rebates use the codes listed</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Up to $279 (gifts+rebates); $130 cash-only</t>
+          <t>Up to $279 in gifts &amp; rebates (cash-only up to $150)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3499,7 +3375,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3509,7 +3385,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3526,22 +3402,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates bundle</t>
+          <t>Gifts &amp; bill rebates</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GIROBCLC / GIROBC30 / MBBC20 / BC10</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gift options need GIRO</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Up to $169</t>
+          <t>Up to $169 in gifts &amp; rebates</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3551,7 +3427,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 Jan 2027</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -3561,7 +3437,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3578,22 +3454,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Luggage set + bill rebate</t>
+          <t>Samsonite luggage set + bill rebate</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TBBCSB30B</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Requires Trust card + GIRO recurring payment</t>
+          <t>Trust card on recurring payment; first 1,000 sign-ups</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>$680 luggage set + up to $50</t>
+          <t>$680 luggage set + $30 rebate</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -3603,7 +3479,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3613,7 +3489,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2 Jul 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3630,22 +3506,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates bundle</t>
+          <t>Bill rebates</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MBBC130 / TGBGN130 / GIROBC100 / BC60</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Amount depends on the code and payment method</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Up to $279</t>
+          <t>Up to $150</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3655,7 +3531,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -3665,7 +3541,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3682,22 +3558,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates bundle</t>
+          <t>Gifts &amp; bill rebates</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GIROBCRC / MBBC130 / TGBGN130 / GIROBC100 / BC60</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>See promotion terms on Senoko's site</t>
+          <t>Gift options need GIRO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Up to $279</t>
+          <t>Up to $279 in gifts &amp; rebates (cash up to $150)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -3707,7 +3583,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3717,7 +3593,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>09 Sep 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3734,22 +3610,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates bundle</t>
+          <t>Luggage set or bill rebates</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TBBCSB30B / MBBC180 / GIROBC150</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>See promotion terms on Senoko Energy's site</t>
+          <t>Luggage set needs a Trust card on recurring payment</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Up to $279</t>
+          <t>$680 luggage set + $30 rebate, or up to $180 in rebates</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3759,7 +3635,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -3769,7 +3645,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>09 Sep 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3786,22 +3662,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bill + card rebate</t>
+          <t>Bill rebate + Maybank card rebate</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NEW125</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$20 card rebate needs a Maybank card on recurring payment</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>$125 + $20 card = up to $145</t>
+          <t>Up to $145 ($125 bill + $20 card)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -3821,7 +3697,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3890,22 +3766,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Bill + card rebate</t>
+          <t>Bill rebate + Maybank card rebate</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NEW100</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$20 card rebate needs a Maybank card on recurring payment</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>$100 + $20 card = up to $120</t>
+          <t>Up to $120 ($100 bill + $20 card)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3925,7 +3801,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3818,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bill rebate</t>
+          <t>Card payment rebate</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3952,12 +3828,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maybank card on recurring payment; first 125 customers</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Up to $10</t>
+          <t>$10</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3967,7 +3843,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -3977,7 +3853,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4004,7 +3880,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Use code ONLINE when you sign up online</t>
+          <t>Sign up online with code ONLINE</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4029,495 +3905,703 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Tuas Power</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>PowerFIX 36</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Bill rebate</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Sign up online with code ONLINE</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>$160</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PowerFIX 25 G+</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Bill rebate</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ONGREEN</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Sign up online with code ONGREEN</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Savvy Saver 24</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>yuu promotion</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>YUU24</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>First 500 sign-ups</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>$50 rebate + 10,000 yuu Points</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Savvy Saver 12</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>yuu promotion</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>YUU12</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>First 500 sign-ups</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>500 yuu Points</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Savvy Saver 36</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>yuu promotion</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>YUU36</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>First 500 sign-ups</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>$50 rebate + 15,000 yuu Points</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Sunny Side-Up 12</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>yuu promotion</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>YUU12</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>First 500 sign-ups</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>500 yuu Points</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Stack It Up 24</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Maybank card rebate</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MBBON140</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>First 30 sign-ups paying by Maybank card on recurring payment</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>31 Dec 2026</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WEEKEND SAVER</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Card payment rebate</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Maybank card on recurring payment</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Up to $20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>31 Dec 2026</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ecoGreen24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bill rebate + Maybank card rebate</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NEW100</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>First 1,000 sign-ups; $20 card rebate needs a Maybank card on recurring payment</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Up to $120 ($100 bill + $20 card)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Keppel Electric</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Save While Sleeping 24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>yuu promotion</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>YUU24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>First 500 sign-ups</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>$50 rebate + 10,000 yuu Points</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>26 Oct 2026</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senoko Energy</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LifeSavvy24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gifts &amp; bill rebates</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GIROBCRC / MBBC130 / TGBGN130 / GIROBC100 / BC60</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gift options need GIRO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Up to $279 in gifts &amp; rebates (cash up to $150)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>31 Dec 2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Senoko Energy</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Classic 60</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Prompt payment discount</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pay each bill in full by the due date (GIRO). On top of the 3% off the tariff, so up to 8% off in total</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Extra 5% off electricity charges</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PacificLight</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tuas Power</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>PowerFIX 12</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Free insurance cover</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Applies to customers on same SP bill</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>12-month Singlife cover (non-cash)</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Choose Home, Travel or Personal Accident cover</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>12 months of Singlife cover (non-cash)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Tuas Power</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>PowerFIX 36</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Bill rebate</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>$160</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>PowerFIX 25 G+</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Bill rebate</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>ONGREEN</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>$100</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Savvy Saver 24</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Bill rebate + referral bonus</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>ATE24</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>First 100 sign-ups; + $20 referral bonus</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>$200 + $20 referral = up to $220</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>30 Sep 2026</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Savvy Saver 12</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Bill rebate</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Up to $10</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Savvy Saver 36</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Bill rebate + referral bonus</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>ATE36</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>First 100 sign-ups; + $20 referral bonus</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>$250 + $20 referral</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>30 Sep 2026</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>20 Aug 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Sunny Side-Up 12</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Bill rebate</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>REC-backed (renewable energy certificate) plan</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Up to $10</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Stack It Up 24</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Bill rebate</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>ATE24</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>First 100 sign-ups</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>30 Sep 2026</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>20 Aug 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Classic 60</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Bill rebate</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>ATE60</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>First 100 sign-ups; spread across 15th &amp; 24th month bills</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>$380</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>PacificLight</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>20 Aug 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Plans with no current sign-up promotion are omitted from this sheet (e.g. trial/time-of-use/tiered/no-frills plans with no rebate).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Link key: Retailer + Plan Name matches the Plans tab. A future Plan ID can replace this text-based join once available.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>This tab is intended for monthly refresh. Updating a promotion here does not require touching the Plans tab, and an expired promotion here does not affect the plan's core pricing data.</t>
         </is>

--- a/data/price-comparison-sheet.xlsx
+++ b/data/price-comparison-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plans" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Plans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Promotions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>29</v>
+        <v>30.9</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>28.5</v>
+        <v>30.4</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>28.9</v>
+        <v>30.63</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bill rebate for new sign-ups</t>
+          <t>Bill rebate for new sign-ups (online only)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sign up online. Current SP Group customers use GENECO200; everyone else GENECO100. The 29.00¢ rate is for the first 1,000 sign-ups</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>$200 (SP customers) / $100 (others)</t>
+          <t>$200 for current SP Group customers (GENECO200); $100 for others (GENECO100)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>2 Nov 2026</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Bill rebate</t>
+          <t>Bill rebate (online sign-ups)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Sign up online; first 250 customers</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>$15</t>
+          <t>$15 (first 250 customers)</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>31 Oct 2026</t>
+          <t>2 Nov 2026</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates</t>
+          <t>Gifts &amp; bill rebates bundle (24-month)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gift options need GIRO; cash-only rebates use the codes listed</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Up to $279 in gifts &amp; rebates (cash-only up to $150)</t>
+          <t>Up to $279 (gift via GIRO + $20 referral); cash-only up to $150</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates</t>
+          <t>Gifts &amp; bill rebates bundle (12-month)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Gift options need GIRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Up to $169 in gifts &amp; rebates</t>
+          <t>Up to $169 (gift via GIRO + $20 referral)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Samsonite luggage set + bill rebate</t>
+          <t>Samsonite luggage set + bill rebate (Trust card recurring payment)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Trust card on recurring payment; first 1,000 sign-ups</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>$680 luggage set + $30 rebate</t>
+          <t>$680 luggage set + $30 bill rebate (first 1,000)</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3516,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Amount depends on the code and payment method</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Up to $150</t>
+          <t>Up to $150 rebate (plan page)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates</t>
+          <t>Gifts &amp; bill rebates bundle (24-month)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Gift options need GIRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Up to $279 in gifts &amp; rebates (cash up to $150)</t>
+          <t>Up to $279; cash rebates up to $150</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Luggage set or bill rebates</t>
+          <t>Samsonite luggage set + bill rebate (Trust card) / 36-month rebates</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Luggage set needs a Trust card on recurring payment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>$680 luggage set + $30 rebate, or up to $180 in rebates</t>
+          <t>$680 luggage set + $30 rebate; or cash rebates up to $180</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>$20 card rebate needs a Maybank card on recurring payment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Up to $145 ($125 bill + $20 card)</t>
+          <t>$125 bill rebate + $20 Maybank card rebate = up to $145</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3776,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>$20 card rebate needs a Maybank card on recurring payment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Up to $120 ($100 bill + $20 card)</t>
+          <t>$100 bill rebate + $20 Maybank card rebate = up to $120</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Card payment rebate</t>
+          <t>Maybank recurring card payment rebate</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Maybank card on recurring payment; first 125 customers</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>$10 bill rebate (first 125)</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4026,22 +4026,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>yuu promotion</t>
+          <t>Payback deal: S$228 rebate on 3rd-month bill (first 100)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>YUU24</t>
+          <t>GETBACK24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>First 500 sign-ups</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>$50 rebate + 10,000 yuu Points</t>
+          <t>$228</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4130,22 +4130,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>yuu promotion</t>
+          <t>Payback deal: S$268 rebate on 3rd-month bill (first 100)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>YUU36</t>
+          <t>GETBACK36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>First 500 sign-ups</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>$50 rebate + 15,000 yuu Points</t>
+          <t>$268</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4234,22 +4234,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Maybank card rebate</t>
+          <t>Payback deal: S$228 rebate on 3rd-month bill (first 100)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MBBON140</t>
+          <t>GETBACK24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>First 30 sign-ups paying by Maybank card on recurring payment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>$140</t>
+          <t>$228</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Card payment rebate</t>
+          <t>Maybank recurring card payment rebate</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maybank card on recurring payment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Up to $20</t>
+          <t>Up to $20 bill rebate</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>First 1,000 sign-ups; $20 card rebate needs a Maybank card on recurring payment</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Up to $120 ($100 bill + $20 card)</t>
+          <t>$100 bill rebate (first 1,000) + $20 Maybank card rebate = up to $120</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4390,22 +4390,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yuu promotion</t>
+          <t>Payback deal: S$228 rebate on 3rd-month bill (first 100)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>YUU24</t>
+          <t>GETBACK24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>First 500 sign-ups</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>$50 rebate + 10,000 yuu Points</t>
+          <t>$228</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>26 Oct 2026</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4425,39 +4425,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senoko Energy</t>
+          <t>PacificLight</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LifeSavvy24</t>
+          <t>Classic 60</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gifts &amp; bill rebates</t>
+          <t>Prompt payment discount</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GIROBCRC / MBBC130 / TGBGN130 / GIROBC100 / BC60</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gift options need GIRO</t>
+          <t>Pay each bill in full by the due date (GIRO). On top of the 3% off the tariff, so up to 8% off in total</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Up to $279 in gifts &amp; rebates (cash up to $150)</t>
+          <t>Extra 5% off electricity charges</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4467,49 +4467,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>31 Dec 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Senoko Energy</t>
+          <t>PacificLight</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PacificLight</t>
+          <t>Senoko Energy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Classic 60</t>
+          <t>LifeSavvy24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prompt payment discount</t>
+          <t>Gifts &amp; bill rebates bundle (24-month)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GIROBCRC / MBBC130 / TGBGN130 / GIROBC100 / BC60</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pay each bill in full by the due date (GIRO). On top of the 3% off the tariff, so up to 8% off in total</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Extra 5% off electricity charges</t>
+          <t>Up to $279; cash rebates up to $150</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4519,89 +4519,37 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PacificLight</t>
+          <t>Senoko Energy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>PowerFIX 12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Free insurance cover</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Choose Home, Travel or Personal Accident cover</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>12 months of Singlife cover (non-cash)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Tuas Power</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>12 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Plans with no current sign-up promotion are omitted from this sheet (e.g. trial/time-of-use/tiered/no-frills plans with no rebate).</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Plans with no current sign-up promotion are omitted from this sheet (e.g. trial/time-of-use/tiered/no-frills plans with no rebate).</t>
+          <t>Link key: Retailer + Plan Name matches the Plans tab. A future Plan ID can replace this text-based join once available.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Link key: Retailer + Plan Name matches the Plans tab. A future Plan ID can replace this text-based join once available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>This tab is intended for monthly refresh. Updating a promotion here does not require touching the Plans tab, and an expired promotion here does not affect the plan's core pricing data.</t>
         </is>

--- a/data/price-comparison-sheet.xlsx
+++ b/data/price-comparison-sheet.xlsx
@@ -1538,12 +1538,12 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Waived for Singapore Citizens and PRs; required for pass holders (amount set by retailer)</t>
+          <t>Billed on your first bill for all new sign-ups: HDB 1–2 room S$50; HDB 3–5 room, Executive or Jumbo S$90; condo or EC S$120; other premises (e.g. shophouse) S$190; landed S$220.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Days left in contract × your average daily charge over the past 12 months</t>
+          <t>30% of your average daily charge over the last 2 months, for each day left in the contract.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>$50–$200 depending on dwelling type</t>
+          <t>None at sign-up if you already have an SP Services account. Otherwise SP Services sets the amount and bills it on your first bill.</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Charged per remaining month; amount depends on home type (see retailer terms)</t>
+          <t>For each month left in the contract: HDB 1-room S$10, 2-room S$15, 3-room S$20, 4-room S$30, 5-room S$35, Executive S$40, private apartment S$40, terrace S$70, semi-detached S$95, bungalow S$200. Waived if you move home (with proof).</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>$50–$200 depending on dwelling type</t>
+          <t>None at sign-up if you already have an SP Services account. Otherwise SP Services sets the amount and bills it on your first bill.</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>Charged per remaining month; amount depends on home type (see retailer terms)</t>
+          <t>For each month left in the contract: HDB 1-room S$10, 2-room S$15, 3-room S$20, 4-room S$30, 5-room S$35, Executive S$40, private apartment S$40, terrace S$70, semi-detached S$95, bungalow S$200. Waived if you move home (with proof).</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4533,7 +4533,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>

--- a/data/price-comparison-sheet.xlsx
+++ b/data/price-comparison-sheet.xlsx
@@ -45,7 +45,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F6FA"/>
         <bgColor rgb="FFF2F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +115,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,12 +691,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3130,34 +3141,89 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1"/>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>* Discount (%) marked with an asterisk denotes a cents-off-tariff figure (not a true percentage) as published by the retailer.</t>
-        </is>
-      </c>
-    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Flo Energy</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Fixed 12</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>To be confirmed by Flo Energy</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>To be confirmed by Flo Energy</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>SAMPLE ROW for the Flo Energy demo (26 Oct 2026): made-up estimate, not a published Flo Energy plan. Delete this row after the demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1"/>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Security Deposit Note: Deposit amounts may vary according to residential type, customer status and/or payment arrangement.</t>
+          <t>* Discount (%) marked with an asterisk denotes a cents-off-tariff figure (not a true percentage) as published by the retailer.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>Security Deposit Note: Deposit amounts may vary according to residential type, customer status and/or payment arrangement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>This sheet only includes product rates and other fact sheet information, for more information on promotions, please check the promotions sheet.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1"/>
     <row r="49" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/data/price-comparison-sheet.xlsx
+++ b/data/price-comparison-sheet.xlsx
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>29</v>
+        <v>30.5</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>30.5</v>
+        <v>31.15</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>28.9</v>
+        <v>29.95</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>29.68</v>
+        <v>30.88</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>20.05</v>
+        <v>21.05</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>36.95</v>
+        <v>37.95</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4599,6 +4599,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>

--- a/data/price-comparison-sheet.xlsx
+++ b/data/price-comparison-sheet.xlsx
@@ -696,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3141,84 +3141,29 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Flo Energy</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Fixed 12</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>To be confirmed by Flo Energy</t>
-        </is>
-      </c>
-      <c r="K44" s="8" t="inlineStr">
-        <is>
-          <t>To be confirmed by Flo Energy</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>SAMPLE ROW for the Flo Energy demo (26 Oct 2026): made-up estimate, not a published Flo Energy plan. Delete this row after the demo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>* Discount (%) marked with an asterisk denotes a cents-off-tariff figure (not a true percentage) as published by the retailer.</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>* Discount (%) marked with an asterisk denotes a cents-off-tariff figure (not a true percentage) as published by the retailer.</t>
+          <t>Security Deposit Note: Deposit amounts may vary according to residential type, customer status and/or payment arrangement.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Security Deposit Note: Deposit amounts may vary according to residential type, customer status and/or payment arrangement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
           <t>This sheet only includes product rates and other fact sheet information, for more information on promotions, please check the promotions sheet.</t>
         </is>
       </c>
     </row>
+    <row r="48" ht="30" customHeight="1"/>
     <row r="49" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4599,7 +4544,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
